--- a/Dados/table_PROD_RS_1.xlsx
+++ b/Dados/table_PROD_RS_1.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -27448,7 +27448,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -30378,7 +30378,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -33500,7 +33500,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -45988,7 +45988,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -48966,7 +48966,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
@@ -51944,7 +51944,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SETOR EMPRESARIAL NÃO-AGRÍCOLA</t>
         </is>
       </c>
     </row>
